--- a/assets/constructions/examples/ctd_arbm_shellchuck.xlsx
+++ b/assets/constructions/examples/ctd_arbm_shellchuck.xlsx
@@ -1,13 +1,13 @@
 
 <file path=xl/workbook.xml><?xml version="1.0" encoding="utf-8"?>
-<workbook xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main">
+<workbook xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main">
   <workbookPr/>
   <workbookProtection/>
   <bookViews>
     <workbookView visibility="visible" minimized="0" showHorizontalScroll="1" showVerticalScroll="1" showSheetTabs="1" tabRatio="600" firstSheet="0" activeTab="0" autoFilterDateGrouping="1"/>
   </bookViews>
   <sheets>
-    <sheet xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" name="ctd" sheetId="1" state="visible" r:id="rId1"/>
+    <sheet name="ctd" sheetId="1" state="visible" r:id="rId1"/>
   </sheets>
   <definedNames/>
   <calcPr calcId="124519" fullCalcOnLoad="1"/>
@@ -425,7 +425,7 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:AF6"/>
+  <dimension ref="A1:AK6"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <sheetData>
     <row r="1">
@@ -589,67 +589,82 @@
           <t>releasepack</t>
         </is>
       </c>
+      <c r="AG1" s="1" t="inlineStr">
+        <is>
+          <t>lcs</t>
+        </is>
+      </c>
+      <c r="AH1" s="1" t="inlineStr">
+        <is>
+          <t>pricevalue</t>
+        </is>
+      </c>
+      <c r="AI1" s="1" t="inlineStr">
+        <is>
+          <t>pricecurrency</t>
+        </is>
+      </c>
+      <c r="AJ1" s="1" t="inlineStr">
+        <is>
+          <t>pricevalue_rub</t>
+        </is>
+      </c>
+      <c r="AK1" s="1" t="inlineStr">
+        <is>
+          <t>lscws</t>
+        </is>
+      </c>
     </row>
     <row r="2">
       <c r="A2" t="inlineStr">
         <is>
-          <t>BT50-FMB27-250</t>
+          <t>SK50-SMA22-120</t>
         </is>
       </c>
       <c r="B2" t="inlineStr">
         <is>
-          <t>DEREK</t>
+          <t>YG1</t>
         </is>
       </c>
       <c r="C2" t="inlineStr">
         <is>
-          <t>Оправки для торцевых фрез FMB</t>
+          <t>SMA SHELL MILL ARBOR</t>
         </is>
       </c>
       <c r="D2" t="inlineStr"/>
       <c r="E2" t="n">
-        <v>250</v>
-      </c>
-      <c r="F2" t="n">
-        <v>250</v>
-      </c>
-      <c r="G2" t="n">
-        <v>60</v>
-      </c>
-      <c r="H2" t="inlineStr"/>
+        <v>120</v>
+      </c>
+      <c r="F2" t="inlineStr"/>
+      <c r="G2" t="inlineStr"/>
+      <c r="H2" t="n">
+        <v>40</v>
+      </c>
       <c r="I2" t="inlineStr"/>
       <c r="J2" t="inlineStr"/>
       <c r="K2" t="inlineStr"/>
-      <c r="L2" t="inlineStr"/>
+      <c r="L2" t="n">
+        <v>19</v>
+      </c>
       <c r="M2" t="inlineStr"/>
       <c r="N2" t="inlineStr"/>
-      <c r="O2" t="n">
-        <v>60</v>
-      </c>
+      <c r="O2" t="inlineStr"/>
       <c r="P2" t="b">
         <v>0</v>
       </c>
       <c r="Q2" t="inlineStr"/>
-      <c r="R2" t="inlineStr">
-        <is>
-          <t>ISO_6462:FDAxx027</t>
-        </is>
-      </c>
+      <c r="R2" t="inlineStr"/>
       <c r="S2" t="inlineStr">
         <is>
-          <t>ISO_6462:FDAxx027</t>
-        </is>
-      </c>
-      <c r="T2" t="inlineStr">
-        <is>
-          <t>DEREK</t>
-        </is>
-      </c>
+          <t>ISO_6462:FDAxx022</t>
+        </is>
+      </c>
+      <c r="T2" t="inlineStr"/>
       <c r="U2" t="n">
-        <v>27</v>
+        <v>22</v>
       </c>
       <c r="V2" t="n">
-        <v>27</v>
+        <v>22</v>
       </c>
       <c r="W2" t="n">
         <v>0</v>
@@ -657,128 +672,150 @@
       <c r="X2" t="n">
         <v>0</v>
       </c>
-      <c r="Y2" t="inlineStr"/>
-      <c r="Z2" t="inlineStr"/>
+      <c r="Y2" t="b">
+        <v>0</v>
+      </c>
+      <c r="Z2" t="n">
+        <v>15000</v>
+      </c>
       <c r="AA2" t="inlineStr">
         <is>
-          <t>JIS_B_6339_MAS_403:BT50</t>
+          <t>DIN_69871:SK50</t>
         </is>
       </c>
       <c r="AB2" t="inlineStr"/>
-      <c r="AC2" t="inlineStr"/>
+      <c r="AC2" t="inlineStr">
+        <is>
+          <t>DIN 69871</t>
+        </is>
+      </c>
       <c r="AD2" t="n">
-        <v>8.51</v>
+        <v>4.4</v>
       </c>
       <c r="AE2" t="n">
         <v>0</v>
       </c>
       <c r="AF2" t="inlineStr">
         <is>
-          <t>2019/DEREK Металлорежущий инструмент и оснастка</t>
-        </is>
-      </c>
+          <t>2021/YG1-TOOLING</t>
+        </is>
+      </c>
+      <c r="AG2" t="n">
+        <v>1</v>
+      </c>
+      <c r="AH2" t="inlineStr"/>
+      <c r="AI2" t="inlineStr"/>
+      <c r="AJ2" t="inlineStr"/>
+      <c r="AK2" t="inlineStr"/>
     </row>
     <row r="3">
       <c r="A3" t="inlineStr">
         <is>
-          <t>A1B05-40 16 100</t>
+          <t>SK50-FMB32-150</t>
         </is>
       </c>
       <c r="B3" t="inlineStr">
         <is>
-          <t>SANDVIK</t>
+          <t>LIKON</t>
         </is>
       </c>
       <c r="C3" t="inlineStr"/>
       <c r="D3" t="inlineStr"/>
-      <c r="E3" t="n">
-        <v>100</v>
-      </c>
+      <c r="E3" t="inlineStr"/>
       <c r="F3" t="inlineStr"/>
-      <c r="G3" t="inlineStr"/>
-      <c r="H3" t="n">
-        <v>36</v>
-      </c>
+      <c r="G3" t="n">
+        <v>78</v>
+      </c>
+      <c r="H3" t="inlineStr"/>
       <c r="I3" t="inlineStr"/>
       <c r="J3" t="inlineStr"/>
       <c r="K3" t="inlineStr"/>
-      <c r="L3" t="n">
-        <v>17</v>
-      </c>
+      <c r="L3" t="inlineStr"/>
       <c r="M3" t="inlineStr"/>
       <c r="N3" t="inlineStr"/>
-      <c r="O3" t="inlineStr"/>
+      <c r="O3" t="n">
+        <v>78</v>
+      </c>
       <c r="P3" t="b">
         <v>0</v>
       </c>
-      <c r="Q3" t="inlineStr"/>
-      <c r="R3" t="inlineStr"/>
+      <c r="Q3" t="n">
+        <v>97.5</v>
+      </c>
+      <c r="R3" t="inlineStr">
+        <is>
+          <t>ISO_6462:FDAxx032</t>
+        </is>
+      </c>
       <c r="S3" t="inlineStr">
         <is>
-          <t>ISO_6462:FDAxx016</t>
-        </is>
-      </c>
-      <c r="T3" t="inlineStr"/>
+          <t>ISO_6462:FDAxx032</t>
+        </is>
+      </c>
+      <c r="T3" t="inlineStr">
+        <is>
+          <t>LIKON</t>
+        </is>
+      </c>
       <c r="U3" t="n">
-        <v>40</v>
+        <v>32</v>
       </c>
       <c r="V3" t="n">
-        <v>16</v>
+        <v>32</v>
       </c>
       <c r="W3" t="n">
-        <v>7</v>
+        <v>0</v>
       </c>
       <c r="X3" t="n">
-        <v>1</v>
-      </c>
-      <c r="Y3" t="b">
-        <v>0</v>
-      </c>
+        <v>0</v>
+      </c>
+      <c r="Y3" t="inlineStr"/>
       <c r="Z3" t="inlineStr"/>
       <c r="AA3" t="inlineStr">
         <is>
-          <t>DIN_69871:SK40</t>
-        </is>
-      </c>
-      <c r="AB3" t="inlineStr"/>
+          <t>DIN_69871:SK50</t>
+        </is>
+      </c>
+      <c r="AB3" t="inlineStr">
+        <is>
+          <t>M16</t>
+        </is>
+      </c>
       <c r="AC3" t="inlineStr"/>
-      <c r="AD3" t="n">
-        <v>1.8</v>
-      </c>
+      <c r="AD3" t="inlineStr"/>
       <c r="AE3" t="n">
         <v>0</v>
       </c>
       <c r="AF3" t="inlineStr">
         <is>
-          <t>2022/coromant web-site</t>
-        </is>
-      </c>
+          <t>2022/LIKON Инструментальный каталог</t>
+        </is>
+      </c>
+      <c r="AG3" t="n">
+        <v>1</v>
+      </c>
+      <c r="AH3" t="inlineStr"/>
+      <c r="AI3" t="inlineStr"/>
+      <c r="AJ3" t="inlineStr"/>
+      <c r="AK3" t="inlineStr"/>
     </row>
     <row r="4">
       <c r="A4" t="inlineStr">
         <is>
-          <t>BT40-FMB32-45</t>
+          <t>SK30-FMB22-35</t>
         </is>
       </c>
       <c r="B4" t="inlineStr">
         <is>
-          <t>DEREK</t>
-        </is>
-      </c>
-      <c r="C4" t="inlineStr">
-        <is>
-          <t>Оправки для торцевых фрез FMB</t>
-        </is>
-      </c>
+          <t>LIKON</t>
+        </is>
+      </c>
+      <c r="C4" t="inlineStr"/>
       <c r="D4" t="inlineStr"/>
-      <c r="E4" t="n">
-        <v>45</v>
-      </c>
-      <c r="F4" t="n">
-        <v>45</v>
-      </c>
+      <c r="E4" t="inlineStr"/>
+      <c r="F4" t="inlineStr"/>
       <c r="G4" t="n">
-        <v>78</v>
+        <v>48</v>
       </c>
       <c r="H4" t="inlineStr"/>
       <c r="I4" t="inlineStr"/>
@@ -788,32 +825,34 @@
       <c r="M4" t="inlineStr"/>
       <c r="N4" t="inlineStr"/>
       <c r="O4" t="n">
-        <v>78</v>
+        <v>48</v>
       </c>
       <c r="P4" t="b">
         <v>0</v>
       </c>
-      <c r="Q4" t="inlineStr"/>
+      <c r="Q4" t="n">
+        <v>50</v>
+      </c>
       <c r="R4" t="inlineStr">
         <is>
-          <t>ISO_6462:FDAxx032</t>
+          <t>ISO_6462:FDAxx022</t>
         </is>
       </c>
       <c r="S4" t="inlineStr">
         <is>
-          <t>ISO_6462:FDAxx032</t>
+          <t>ISO_6462:FDAxx022</t>
         </is>
       </c>
       <c r="T4" t="inlineStr">
         <is>
-          <t>DEREK</t>
+          <t>LIKON</t>
         </is>
       </c>
       <c r="U4" t="n">
-        <v>32</v>
+        <v>22</v>
       </c>
       <c r="V4" t="n">
-        <v>32</v>
+        <v>22</v>
       </c>
       <c r="W4" t="n">
         <v>0</v>
@@ -825,27 +864,36 @@
       <c r="Z4" t="inlineStr"/>
       <c r="AA4" t="inlineStr">
         <is>
-          <t>JIS_B_6339_MAS_403:BT40</t>
-        </is>
-      </c>
-      <c r="AB4" t="inlineStr"/>
+          <t>DIN_69871:SK30</t>
+        </is>
+      </c>
+      <c r="AB4" t="inlineStr">
+        <is>
+          <t>M10</t>
+        </is>
+      </c>
       <c r="AC4" t="inlineStr"/>
-      <c r="AD4" t="n">
-        <v>1.87</v>
-      </c>
+      <c r="AD4" t="inlineStr"/>
       <c r="AE4" t="n">
         <v>0</v>
       </c>
       <c r="AF4" t="inlineStr">
         <is>
-          <t>2019/DEREK Металлорежущий инструмент и оснастка</t>
-        </is>
-      </c>
+          <t>2022/LIKON Инструментальный каталог</t>
+        </is>
+      </c>
+      <c r="AG4" t="n">
+        <v>1</v>
+      </c>
+      <c r="AH4" t="inlineStr"/>
+      <c r="AI4" t="inlineStr"/>
+      <c r="AJ4" t="inlineStr"/>
+      <c r="AK4" t="inlineStr"/>
     </row>
     <row r="5">
       <c r="A5" t="inlineStr">
         <is>
-          <t>HSK100A-SMA32-50</t>
+          <t>BT50-SMA40-75</t>
         </is>
       </c>
       <c r="B5" t="inlineStr">
@@ -860,18 +908,18 @@
       </c>
       <c r="D5" t="inlineStr"/>
       <c r="E5" t="n">
-        <v>50</v>
+        <v>75</v>
       </c>
       <c r="F5" t="inlineStr"/>
       <c r="G5" t="inlineStr"/>
       <c r="H5" t="n">
-        <v>58</v>
+        <v>70</v>
       </c>
       <c r="I5" t="inlineStr"/>
       <c r="J5" t="inlineStr"/>
       <c r="K5" t="inlineStr"/>
       <c r="L5" t="n">
-        <v>24</v>
+        <v>27</v>
       </c>
       <c r="M5" t="inlineStr"/>
       <c r="N5" t="inlineStr"/>
@@ -883,21 +931,21 @@
       <c r="R5" t="inlineStr"/>
       <c r="S5" t="inlineStr">
         <is>
-          <t>ISO_6462:FDAxx032</t>
+          <t>ISO_6462:FDAxx040</t>
         </is>
       </c>
       <c r="T5" t="inlineStr"/>
       <c r="U5" t="n">
-        <v>32</v>
+        <v>40</v>
       </c>
       <c r="V5" t="n">
-        <v>32</v>
+        <v>40</v>
       </c>
       <c r="W5" t="n">
-        <v>1</v>
+        <v>0</v>
       </c>
       <c r="X5" t="n">
-        <v>1</v>
+        <v>0</v>
       </c>
       <c r="Y5" t="b">
         <v>0</v>
@@ -907,18 +955,12 @@
       </c>
       <c r="AA5" t="inlineStr">
         <is>
-          <t>ISO_12164_1_2013:HSK100A</t>
+          <t>JIS_B_6339_MAS_403:BT50</t>
         </is>
       </c>
       <c r="AB5" t="inlineStr"/>
-      <c r="AC5" t="inlineStr">
-        <is>
-          <t>DIN 69893</t>
-        </is>
-      </c>
-      <c r="AD5" t="n">
-        <v>2.6</v>
-      </c>
+      <c r="AC5" t="inlineStr"/>
+      <c r="AD5" t="inlineStr"/>
       <c r="AE5" t="n">
         <v>0</v>
       </c>
@@ -927,32 +969,31 @@
           <t>2021/YG1-TOOLING</t>
         </is>
       </c>
+      <c r="AG5" t="n">
+        <v>1</v>
+      </c>
+      <c r="AH5" t="inlineStr"/>
+      <c r="AI5" t="inlineStr"/>
+      <c r="AJ5" t="inlineStr"/>
+      <c r="AK5" t="inlineStr"/>
     </row>
     <row r="6">
       <c r="A6" t="inlineStr">
         <is>
-          <t>HSK50A-FMB22-60</t>
+          <t>BT40-FMB27-45</t>
         </is>
       </c>
       <c r="B6" t="inlineStr">
         <is>
-          <t>DEREK</t>
-        </is>
-      </c>
-      <c r="C6" t="inlineStr">
-        <is>
-          <t>Оправки для торцевых фрез HSK-A-FMB</t>
-        </is>
-      </c>
+          <t>LIKON</t>
+        </is>
+      </c>
+      <c r="C6" t="inlineStr"/>
       <c r="D6" t="inlineStr"/>
-      <c r="E6" t="n">
+      <c r="E6" t="inlineStr"/>
+      <c r="F6" t="inlineStr"/>
+      <c r="G6" t="n">
         <v>60</v>
-      </c>
-      <c r="F6" t="n">
-        <v>60</v>
-      </c>
-      <c r="G6" t="n">
-        <v>48</v>
       </c>
       <c r="H6" t="inlineStr"/>
       <c r="I6" t="inlineStr"/>
@@ -962,34 +1003,34 @@
       <c r="M6" t="inlineStr"/>
       <c r="N6" t="inlineStr"/>
       <c r="O6" t="n">
-        <v>48</v>
+        <v>60</v>
       </c>
       <c r="P6" t="b">
         <v>0</v>
       </c>
       <c r="Q6" t="n">
-        <v>50</v>
+        <v>63</v>
       </c>
       <c r="R6" t="inlineStr">
         <is>
-          <t>DER_FMB22</t>
+          <t>ISO_6462:FDAxx027</t>
         </is>
       </c>
       <c r="S6" t="inlineStr">
         <is>
-          <t>ISO_6462:FDAxx022</t>
+          <t>ISO_6462:FDAxx027</t>
         </is>
       </c>
       <c r="T6" t="inlineStr">
         <is>
-          <t>DEREK</t>
+          <t>LIKON</t>
         </is>
       </c>
       <c r="U6" t="n">
-        <v>22</v>
+        <v>27</v>
       </c>
       <c r="V6" t="n">
-        <v>22</v>
+        <v>27</v>
       </c>
       <c r="W6" t="n">
         <v>0</v>
@@ -1001,22 +1042,31 @@
       <c r="Z6" t="inlineStr"/>
       <c r="AA6" t="inlineStr">
         <is>
-          <t>ISO_12164_1_2013:HSK50A</t>
-        </is>
-      </c>
-      <c r="AB6" t="inlineStr"/>
+          <t>JIS_B_6339_MAS_403:BT40</t>
+        </is>
+      </c>
+      <c r="AB6" t="inlineStr">
+        <is>
+          <t>M12</t>
+        </is>
+      </c>
       <c r="AC6" t="inlineStr"/>
-      <c r="AD6" t="n">
+      <c r="AD6" t="inlineStr"/>
+      <c r="AE6" t="n">
+        <v>0</v>
+      </c>
+      <c r="AF6" t="inlineStr">
+        <is>
+          <t>2022/LIKON Инструментальный каталог</t>
+        </is>
+      </c>
+      <c r="AG6" t="n">
         <v>1</v>
       </c>
-      <c r="AE6" t="n">
-        <v>0</v>
-      </c>
-      <c r="AF6" t="inlineStr">
-        <is>
-          <t>2019/DEREK Металлорежущий инструмент и оснастка</t>
-        </is>
-      </c>
+      <c r="AH6" t="inlineStr"/>
+      <c r="AI6" t="inlineStr"/>
+      <c r="AJ6" t="inlineStr"/>
+      <c r="AK6" t="inlineStr"/>
     </row>
   </sheetData>
   <pageMargins left="0.75" right="0.75" top="1" bottom="1" header="0.5" footer="0.5"/>
